--- a/nr-update-fr-core-dependency/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/nr-update-fr-core-dependency/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:52:43+00:00</t>
+    <t>2024-04-03T13:38:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-fr-core-dependency/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/nr-update-fr-core-dependency/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-3</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:38:42+00:00</t>
+    <t>2024-04-03T14:06:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
